--- a/kp-calc/data/prices-draft.xlsx
+++ b/kp-calc/data/prices-draft.xlsx
@@ -10,13 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как читать" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Группы" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЛДСП корпус" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кромка" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фасады плитные" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фасады покупные" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Столешницы" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Стеновые панели" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Плинтус" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фурнитура" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фасады плитные" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фасады покупные" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Столешницы" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Стеновые панели" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Плинтус" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фурнитура" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -491,1574 +490,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Покупное (столешницы и стеновые Троя ×0,6, фасады Ботаника ×0,8): книга переводила прайс поставщика в цену закупки. Похоже на скидку дилера — подтвердить. У кромки цен нет: в книге кромка в цену не входила, теперь она заложена в +150 ₽/м² ЛДСП.</t>
+          <t>Кромка отдельно не считается: она заложена в +150 ₽/м² к себестоимости ЛДСП.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Фурнитура — цены закупки из книги (50 позиций). Владелец пришлёт актуальные цены; их можно вписать прямо сюда.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Группа</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Позиция / артикул</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Цена поставщика, ₽</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Цена в книге, ₽</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Своё производство</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Правило в книге</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Петли</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Петля "Firmax Adevenced Plus" (с доводчиком)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>180</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Петли</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Петля "Firmax Adevenced Plus" (в угловой шкаф)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>350</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Петли</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Петля "Blum" (с доводчиком)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>450</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Петли</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Петля "Blum" (В угловой шкаф)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>590</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Подъёмники</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>газлифт</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>250</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Подъёмники</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Aventos HF</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>16085</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Подъёмники</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Aventos HS</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>16569</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Подъёмники</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Aventos HL</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>17245</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>закупка</t>
+          <t>Покупное (столешницы и стеновые Троя ×0,6, фасады Ботаника ×0,8): книга переводила прайс поставщика в цену закупки. Похоже на скидку дилера — подтвердить.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Подъёмники</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Aventos HK top</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>8800</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Подъёмники</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Aventos HK top tipon</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10422</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Подъёмники</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Aventos HK XS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4366</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Подъёмники</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Aventos HK XS tipon</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4704</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Ручки и открывание</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Интегрировання ручка</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>900</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Ручки и открывание</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Tip on Boyard</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>350</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Ручки и открывание</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Tip on Blum</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>900</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Профиль Gola</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Gola Алюминий</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Профиль Gola</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Gola Черный</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Профиль Gola</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Gola Белый</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Профиль Gola</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Gola Золото</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ХДФ (задняя стенка)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ХДФ (серый, черный, белый)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>400</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Firmax скрытого монтажа</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Firmax скрытого монтажа от нажатия</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1900</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Alphaluх (метал/стекло)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>2920</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Alphaluх (метал/стекло) от нажатия</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>3910</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Скрытогомонтажа чс.выд Blum</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1950</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Скрытогомонтажа пол.выд Blum</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>3955</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Скрытогомонтажа пол.выд tipon Blum</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>6692</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Тандембокс antaro Blum</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>7027</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Леграбокс Blum</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>9734</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Внут.Тандембокс antaro Blum</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>8798</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Внут.Леграбокс Blum</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>12689</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Тандембокс antaro Blum tipon</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10345</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Леграбокс Blum tipon</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>13326</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Ящики и направляющие</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Подсветка для Alphaluх стеклянного ящика</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Сушки и корзины</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Сушка SU02/500</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>2686</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Сушки и корзины</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Сушка SU02/600</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>2928</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Сушки и корзины</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Сушка SU02/700</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>3383</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Сушки и корзины</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Сушка SU02/800</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>3808</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Сушки и корзины</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Сушка SU02/900</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>4234</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Сушки и корзины</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Выдвижная корзина-сушка MIRA KRS06/1/3/600</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>9600</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Сушки и корзины</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Выдвижная корзина-сушка MIRA KRS06/1/3/800</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11250</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Сушки и корзины</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Выдвижная корзина-сушка MIRA KRS06/1/3/900</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>12150</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Бутылочницы (карго)</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Boyard 150 KR08</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>4989</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Бутылочницы (карго)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Boyard 200 KR08</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>5855</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Бутылочницы (карго)</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Boyard 300 KR19</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>8750</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Плинтус</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Плинтус низкий</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>500</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Плинтус</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Плинтус высокий</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>650</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Цоколь</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Цоколь 100мм</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>475</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Цоколь</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Цоколь 150мм</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>680</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Крепёж (крабы)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Комплект крабов</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>260</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>закупка</t>
+          <t>Фурнитура — цены закупки из книги (50 позиций). Владелец пришлёт актуальные цены; их можно вписать прямо сюда.</t>
         </is>
       </c>
     </row>
@@ -2073,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2335,35 +781,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Кромка</t>
+          <t>Фасады плитные</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Кромка</t>
+          <t>Пластик на ЛДСП гр. 1–3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>уточнить</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Прайс1 «Кромка»</t>
+          <t>Прайс1 «Пластик_гр.1_3_ЛДСП»</t>
         </is>
       </c>
     </row>
@@ -2375,7 +816,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Пластик на ЛДСП гр. 1–3</t>
+          <t>Пластик на ЛДСП гр. 4–6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2389,11 +830,11 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Прайс1 «Пластик_гр.1_3_ЛДСП»</t>
+          <t>Прайс1 «Пластик_гр.4_6_ЛДСП»</t>
         </is>
       </c>
     </row>
@@ -2405,7 +846,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Пластик на ЛДСП гр. 4–6</t>
+          <t>Пластик на ЛДСП гр. 7–10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2419,11 +860,11 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>225</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Прайс1 «Пластик_гр.4_6_ЛДСП»</t>
+          <t>Прайс1 «Пластик_гр.7_10_ЛДСП»</t>
         </is>
       </c>
     </row>
@@ -2435,7 +876,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Пластик на ЛДСП гр. 7–10</t>
+          <t>Пластик на ЛДСП гр. 11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2449,11 +890,11 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>225</v>
+        <v>4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Прайс1 «Пластик_гр.7_10_ЛДСП»</t>
+          <t>Прайс1 «Пластик_гр.11_ЛДСП»</t>
         </is>
       </c>
     </row>
@@ -2465,7 +906,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Пластик на ЛДСП гр. 11</t>
+          <t>Пластик на МДФ гр. 1–3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2479,11 +920,11 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Прайс1 «Пластик_гр.11_ЛДСП»</t>
+          <t>Прайс1 «Пластик_гр.1_3_МДФ»</t>
         </is>
       </c>
     </row>
@@ -2495,7 +936,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Пластик на МДФ гр. 1–3</t>
+          <t>Пластик на МДФ гр. 4–6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2509,11 +950,11 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Прайс1 «Пластик_гр.1_3_МДФ»</t>
+          <t>Прайс1 «Пластик_гр.4_6_МДФ»</t>
         </is>
       </c>
     </row>
@@ -2525,7 +966,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Пластик на МДФ гр. 4–6</t>
+          <t>Пластик на МДФ гр. 7–10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2539,11 +980,11 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>225</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Прайс1 «Пластик_гр.4_6_МДФ»</t>
+          <t>Прайс1 «Пластик_гр.7_10_МДФ»</t>
         </is>
       </c>
     </row>
@@ -2555,7 +996,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Пластик на МДФ гр. 7–10</t>
+          <t>Пластик на МДФ гр. 11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2569,11 +1010,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>225</v>
+        <v>4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Прайс1 «Пластик_гр.7_10_МДФ»</t>
+          <t>Прайс1 «Пластик_гр.11_МДФ»</t>
         </is>
       </c>
     </row>
@@ -2585,7 +1026,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Пластик на МДФ гр. 11</t>
+          <t>AGT односторонний</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2595,15 +1036,15 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>да</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Прайс1 «Пластик_гр.11_МДФ»</t>
+          <t>Прайс1 «AGT_односторонний»</t>
         </is>
       </c>
     </row>
@@ -2615,7 +1056,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AGT односторонний</t>
+          <t>AGT Supramat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2628,12 +1069,17 @@
           <t>да</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>(E/3,416×1,2+150)×2</t>
+        </is>
+      </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Прайс1 «AGT_односторонний»</t>
+          <t>Прайс1 «AGT_supramat»</t>
         </is>
       </c>
     </row>
@@ -2645,7 +1091,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AGT Supramat</t>
+          <t>ALVIC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2655,20 +1101,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>уточнить</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(E/3,416×1,2+150)×2</t>
+          <t>(E/3,35×1,2+150)×2,4</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Прайс1 «AGT_supramat»</t>
+          <t>Прайс1 «ALVIC»</t>
         </is>
       </c>
     </row>
@@ -2680,7 +1126,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ALVIC</t>
+          <t>Egger Perfect Sense</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2695,15 +1141,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(E/3,35×1,2+150)×2,4</t>
+          <t>(E/3,416×1,2+150)×2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Прайс1 «ALVIC»</t>
+          <t>Прайс1 «Perfect_sence_Egger»</t>
         </is>
       </c>
     </row>
@@ -2715,7 +1161,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Egger Perfect Sense</t>
+          <t>Egger Perfect Sense Smart</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2728,17 +1174,12 @@
           <t>уточнить</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>(E/3,416×1,2+150)×2</t>
-        </is>
-      </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Прайс1 «Perfect_sence_Egger»</t>
+          <t>Прайс1 «Perfect_sence_Smart_Egger»</t>
         </is>
       </c>
     </row>
@@ -2750,7 +1191,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Egger Perfect Sense Smart</t>
+          <t>Egger Perfect Sense TOP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2768,7 +1209,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Прайс1 «Perfect_sence_Smart_Egger»</t>
+          <t>Прайс1 «Perfect_sence_TOP_Egger»</t>
         </is>
       </c>
     </row>
@@ -2780,7 +1221,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Egger Perfect Sense TOP</t>
+          <t>Fenix</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2794,23 +1235,23 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Прайс1 «Perfect_sence_TOP_Egger»</t>
+          <t>Прайс1 «Fenix»</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Фасады плитные</t>
+          <t>Фасады покупные</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fenix</t>
+          <t>Ботаника МДФ 16, обратная белая</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2820,15 +1261,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>E×0,8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Прайс1 «Fenix»</t>
+          <t>Прайс1 «Ботаника_мдф16_обр_белая»</t>
         </is>
       </c>
     </row>
@@ -2840,7 +1286,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ботаника МДФ 16, обратная белая</t>
+          <t>Ботаника МДФ 16, обратная в цвет</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2859,11 +1305,11 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_мдф16_обр_белая»</t>
+          <t>Прайс1 «Ботаника_мдф16_обр_в_цвет»</t>
         </is>
       </c>
     </row>
@@ -2875,7 +1321,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ботаника МДФ 16, обратная в цвет</t>
+          <t>Ботаника ДСП 16, обратная белая</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2886,11 +1332,6 @@
       <c r="D25" t="inlineStr">
         <is>
           <t>нет</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>E×0,8</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2898,7 +1339,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_мдф16_обр_в_цвет»</t>
+          <t>Прайс1 «Ботаника_дсп16_обр_белая»</t>
         </is>
       </c>
     </row>
@@ -2910,7 +1351,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ботаника ДСП 16, обратная белая</t>
+          <t>Ботаника ДСП 16, обратная в цвет</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2928,7 +1369,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_дсп16_обр_белая»</t>
+          <t>Прайс1 «Ботаника_дсп16_обр_в_цвет»</t>
         </is>
       </c>
     </row>
@@ -2940,7 +1381,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ботаника ДСП 16, обратная в цвет</t>
+          <t>Эмаль (матовая, глянец, фрезеровка, патина)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2954,11 +1395,11 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_дсп16_обр_в_цвет»</t>
+          <t>Прайс1 «Эмаль_фрезеровка_сложная»</t>
         </is>
       </c>
     </row>
@@ -2970,7 +1411,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Эмаль (матовая, глянец, фрезеровка, патина)</t>
+          <t>ПВХ Дядя Фёдор</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2984,11 +1425,11 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Прайс1 «Эмаль_фрезеровка_сложная»</t>
+          <t>Прайс1 «ПВХ_ДядяФедор»</t>
         </is>
       </c>
     </row>
@@ -3000,7 +1441,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ПВХ Дядя Фёдор</t>
+          <t>Шпон</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3014,11 +1455,11 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Прайс1 «ПВХ_ДядяФедор»</t>
+          <t>Прайс1 «Шпон»</t>
         </is>
       </c>
     </row>
@@ -3030,7 +1471,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Шпон</t>
+          <t>Массив</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3044,11 +1485,11 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Прайс1 «Шпон»</t>
+          <t>Прайс1 «Массив»</t>
         </is>
       </c>
     </row>
@@ -3060,7 +1501,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Массив</t>
+          <t>Стекло в алюминиевой рамке</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3074,28 +1515,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Прайс1 «Массив»</t>
+          <t>Прайс1 «Стекло_в_Ал_Рамке»</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Фасады покупные</t>
+          <t>Столешницы</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Стекло в алюминиевой рамке</t>
+          <t>Троя 38 мм гр. 1–4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3103,12 +1544,17 @@
           <t>нет</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>E×0,6</t>
+        </is>
+      </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Прайс1 «Стекло_в_Ал_Рамке»</t>
+          <t>Прайс1 «Троя_38мм_гр.1_4»</t>
         </is>
       </c>
     </row>
@@ -3120,7 +1566,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Троя 38 мм гр. 1–4</t>
+          <t>Троя 38 мм гр. 5–7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3139,11 +1585,11 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_38мм_гр.1_4»</t>
+          <t>Прайс1 «Троя_38мм_гр.5_7»</t>
         </is>
       </c>
     </row>
@@ -3155,7 +1601,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Троя 38 мм гр. 5–7</t>
+          <t>Троя 38 мм гр. 8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3174,11 +1620,11 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_38мм_гр.5_7»</t>
+          <t>Прайс1 «Троя_38мм_гр.8»</t>
         </is>
       </c>
     </row>
@@ -3190,7 +1636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Троя 38 мм гр. 8</t>
+          <t>Троя 38 мм гр. 9</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3209,11 +1655,11 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_38мм_гр.8»</t>
+          <t>Прайс1 «Троя_38мм_гр.9»</t>
         </is>
       </c>
     </row>
@@ -3225,7 +1671,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Троя 38 мм гр. 9</t>
+          <t>Троя 38 мм гр. 10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3244,11 +1690,11 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_38мм_гр.9»</t>
+          <t>Прайс1 «Троя_38мм_гр.10»</t>
         </is>
       </c>
     </row>
@@ -3260,7 +1706,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Троя 38 мм гр. 10</t>
+          <t>Троя 38 мм гр. 11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3279,11 +1725,11 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_38мм_гр.10»</t>
+          <t>Прайс1 «Троя_38мм_гр.11»</t>
         </is>
       </c>
     </row>
@@ -3295,7 +1741,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Троя 38 мм гр. 11</t>
+          <t>Ботаника ДСП 38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3314,11 +1760,11 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_38мм_гр.11»</t>
+          <t>Прайс1 «Ботаника_ДСП38»</t>
         </is>
       </c>
     </row>
@@ -3330,7 +1776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ботаника ДСП 38</t>
+          <t>Ботаника ФНР 38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3353,7 +1799,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_ДСП38»</t>
+          <t>Прайс1 «Ботаника_ФНР38»</t>
         </is>
       </c>
     </row>
@@ -3365,7 +1811,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ботаника ФНР 38</t>
+          <t>Ботаника ФНР 18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3388,7 +1834,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_ФНР38»</t>
+          <t>Прайс1 «Ботаника_ФНР18»</t>
         </is>
       </c>
     </row>
@@ -3400,12 +1846,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ботаника ФНР 18</t>
+          <t>Угловой сегмент 38 мм гр. 1–4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3413,17 +1859,12 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>E×0,6</t>
-        </is>
-      </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_ФНР18»</t>
+          <t>Прайс1 «Угловой_сегмент_38мм_гр.1_4»</t>
         </is>
       </c>
     </row>
@@ -3435,7 +1876,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Угловой сегмент 38 мм гр. 1–4</t>
+          <t>Угловой сегмент 38 мм гр. 4–6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3449,11 +1890,11 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Прайс1 «Угловой_сегмент_38мм_гр.1_4»</t>
+          <t>Прайс1 «Угловой_сегмент_38мм_гр.4_6»</t>
         </is>
       </c>
     </row>
@@ -3465,7 +1906,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Угловой сегмент 38 мм гр. 4–6</t>
+          <t>Угловой сегмент 38 мм гр. 7–10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3479,28 +1920,28 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>57</v>
+        <v>220</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Прайс1 «Угловой_сегмент_38мм_гр.4_6»</t>
+          <t>Прайс1 «Угловой_сегмент_38мм_гр.7_10»</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Столешницы</t>
+          <t>Стеновые панели</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Угловой сегмент 38 мм гр. 7–10</t>
+          <t>Троя стеновая гр. 1–4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3508,12 +1949,17 @@
           <t>нет</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>E×0,6</t>
+        </is>
+      </c>
       <c r="F44" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Прайс1 «Угловой_сегмент_38мм_гр.7_10»</t>
+          <t>Прайс1 «Троя_фартук_гр.1_4»</t>
         </is>
       </c>
     </row>
@@ -3525,7 +1971,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Троя стеновая гр. 1–4</t>
+          <t>Троя стеновая гр. 5–7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3544,11 +1990,11 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_фартук_гр.1_4»</t>
+          <t>Прайс1 «Троя_фартук_гр.5_7»</t>
         </is>
       </c>
     </row>
@@ -3560,7 +2006,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Троя стеновая гр. 5–7</t>
+          <t>Троя стеновая гр. 8</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3579,11 +2025,11 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_фартук_гр.5_7»</t>
+          <t>Прайс1 «Троя_фартук_гр.8»</t>
         </is>
       </c>
     </row>
@@ -3595,7 +2041,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Троя стеновая гр. 8</t>
+          <t>Троя стеновая гр. 9</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3614,11 +2060,11 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_фартук_гр.8»</t>
+          <t>Прайс1 «Троя_фартук_гр.9»</t>
         </is>
       </c>
     </row>
@@ -3630,7 +2076,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Троя стеновая гр. 9</t>
+          <t>Троя стеновая гр. 10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3649,11 +2095,11 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_фартук_гр.9»</t>
+          <t>Прайс1 «Троя_фартук_гр.10»</t>
         </is>
       </c>
     </row>
@@ -3665,7 +2111,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Троя стеновая гр. 10</t>
+          <t>Троя стеновая гр. 11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3684,11 +2130,11 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_фартук_гр.10»</t>
+          <t>Прайс1 «Троя_фартук_гр.11»</t>
         </is>
       </c>
     </row>
@@ -3700,7 +2146,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Троя стеновая гр. 11</t>
+          <t>Ботаника ДСП стеновая</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3719,28 +2165,28 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Прайс1 «Троя_фартук_гр.11»</t>
+          <t>Прайс1 «Стеновая_Ботаника_ДСП»</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Стеновые панели</t>
+          <t>Плинтус</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ботаника ДСП стеновая</t>
+          <t>Плинтус</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>шт (3 м)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3748,34 +2194,29 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>E×0,6</t>
-        </is>
-      </c>
       <c r="F51" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Прайс1 «Стеновая_Ботаника_ДСП»</t>
+          <t>Прайс1 «Плинтус_3м_шт»</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Плинтус</t>
+          <t>Фурнитура</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Плинтус</t>
+          <t>Петли</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>шт (3 м)</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3783,12 +2224,17 @@
           <t>нет</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
       <c r="F52" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Прайс1 «Плинтус_3м_шт»</t>
+          <t>Прайс Фурнитура «Петли»</t>
         </is>
       </c>
     </row>
@@ -3800,7 +2246,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Петли</t>
+          <t>Подъёмники</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3819,11 +2265,11 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Петли»</t>
+          <t>Прайс Фурнитура «Подъемный_механизм»</t>
         </is>
       </c>
     </row>
@@ -3835,7 +2281,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Подъёмники</t>
+          <t>Ручки и открывание</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3854,11 +2300,11 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Подъемный_механизм»</t>
+          <t>Прайс Фурнитура «Ручка_верх»</t>
         </is>
       </c>
     </row>
@@ -3870,12 +2316,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ручки и открывание</t>
+          <t>Профиль Gola</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3889,11 +2335,11 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Ручка_верх»</t>
+          <t>Прайс Фурнитура «Профиль_GOLA_G13»</t>
         </is>
       </c>
     </row>
@@ -3905,12 +2351,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Профиль Gola</t>
+          <t>ХДФ (задняя стенка)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3924,11 +2370,11 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Профиль_GOLA_G13»</t>
+          <t>Прайс Фурнитура «ХДФ»</t>
         </is>
       </c>
     </row>
@@ -3940,12 +2386,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ХДФ (задняя стенка)</t>
+          <t>Ящики и направляющие</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3959,11 +2405,11 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «ХДФ»</t>
+          <t>Прайс Фурнитура «Выкатной_механизм»</t>
         </is>
       </c>
     </row>
@@ -3975,12 +2421,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ящики и направляющие</t>
+          <t>Сушки и корзины</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3994,11 +2440,11 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Выкатной_механизм»</t>
+          <t>Прайс Фурнитура «Сушка»</t>
         </is>
       </c>
     </row>
@@ -4010,7 +2456,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Сушки и корзины</t>
+          <t>Бутылочницы (карго)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,11 +2475,11 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Сушка»</t>
+          <t>Прайс Фурнитура «Бутылочница»</t>
         </is>
       </c>
     </row>
@@ -4045,12 +2491,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Бутылочницы (карго)</t>
+          <t>Плинтус</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4064,11 +2510,11 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Бутылочница»</t>
+          <t>Прайс Фурнитура «Плинтус»</t>
         </is>
       </c>
     </row>
@@ -4080,7 +2526,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Плинтус</t>
+          <t>Цоколь</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4103,7 +2549,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Плинтус»</t>
+          <t>Прайс Фурнитура «Цоколь_прайс»</t>
         </is>
       </c>
     </row>
@@ -4115,12 +2561,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Цоколь</t>
+          <t>Крепёж (крабы)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4134,28 +2580,28 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Цоколь_прайс»</t>
+          <t>Прайс Фурнитура «Комплект_крабов»</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Фурнитура</t>
+          <t>Подсветка</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Крепёж (крабы)</t>
+          <t>Лента 24 В, 4000 K (одна позиция)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4165,15 +2611,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>закупка</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
+          <t>вручную</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Комплект_крабов»</t>
+          <t>решение владельца 27.10.2026</t>
         </is>
       </c>
     </row>
@@ -4185,7 +2633,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Лента 24 В, 4000 K (одна позиция)</t>
+          <t>Профиль врезной / накладной</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4210,7 +2658,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>решение владельца 27.10.2026</t>
+          <t>паз включён в цену профиля</t>
         </is>
       </c>
     </row>
@@ -4222,12 +2670,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Профиль врезной / накладной</t>
+          <t>Блоки питания 24 В</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4237,7 +2685,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>вручную</t>
+          <t>подбор по мощности</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4247,7 +2695,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>паз включён в цену профиля</t>
+          <t>цены дать</t>
         </is>
       </c>
     </row>
@@ -4259,7 +2707,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Блоки питания 24 В</t>
+          <t>Выключатели: кнопка, сенсор на взмах, датчик двери</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4274,7 +2722,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>подбор по мощности</t>
+          <t>вручную</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4283,43 +2731,6 @@
         </is>
       </c>
       <c r="G66" t="inlineStr">
-        <is>
-          <t>цены дать</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Подсветка</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Выключатели: кнопка, сенсор на взмах, датчик двери</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>вручную</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
         <is>
           <t>цены дать</t>
         </is>
@@ -18221,2886 +16632,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Группа</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Позиция / артикул</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Цена поставщика, ₽</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Цена в книге, ₽</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Своё производство</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Правило в книге</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Аида табак 0104</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Алюминий 0880</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Антрацит 0777</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Арабика 0779</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Беж-латте 0718</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Бежевый 0715</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Белый 0701</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Белый гладкий 0110</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Белый глянец 0700</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Береза мраморная 0620</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Бук 0264</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Бук Бавария 0265</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Бук Бавария темный 0255</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Бук натуральный 0224</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Бук Тироль 0299</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ваниль 0714</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Венге 0155</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Венге светлый 0140</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Венге темный 0139</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Вишня академия 0390</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Вишня гамильтон 0344</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Вишня Оксфорд 0380</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Вудлайн кремовый 0129</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Вудлайн мокко 0128</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Выбеленное дерево 0150</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Вяз 0617</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Гасиенда черный 0133</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Голубой 0720</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Дуб 0156</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Дуб антик 0113</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Дуб венге 0138</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Дуб галиано 0145</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Дуб горный светлый 0125</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Дуб европейский 0137</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Дуб марсала 0177</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Дуб молочный 0120</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Дуб светлый 0127</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Дуб Светлый венге 0100</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Дуб солнечный 0131</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Дуб сонома 0107</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Дуб феррара 0144</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Дуб шамони светлый 0124</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Дуб шамони темный 0122</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Желтый 0730</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Желтый 0735</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Зебрано 0105</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Зебрано темный 0106</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Зеленый 0765</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Зеленый степной 0763</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Ирис 0760</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Капучино 0170</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Клен танзай 0673</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Коричневый 0707</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Красное дерево 0388</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Красный 0708</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Красный 0740</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Крем 0702</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Кремовый 0715</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Лайм 0733</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Латте 0180</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Лиственница 0212</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Макассар 0111</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Макассар 0188</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Манго 0725</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Махагон Топ 0549</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Металлик 0705</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Микролайм золотой 0850</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Ноче мокко 0502</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Ольха 0491</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Ольха 0492</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Ольха темная 0495</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Оранжевый 0722</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Орех 0504</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Орех 0510</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Орех 0517</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Орех гварнери 0519</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Орех Миланский 0500</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Розовый жемчуг 0870</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Светло-серый 0771</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Серый 0770</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Синий 0711</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Синий 0721</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Слива валис 0340</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Сосна ларедо 0130</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Твист 0811</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Твист серый 0630</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Титан 0883</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Фино бронза 0183</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Черный 0799</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Черный глянец 0709</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Эбони светлый 0165</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Эбони темный 0163</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Яблоко Индия 0512</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Кромка</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Яблоня локарно 0320</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -48167,7 +43698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -50232,7 +45763,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -74267,7 +69798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -87856,7 +83387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -90164,4 +85695,1564 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Позиция / артикул</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Цена поставщика, ₽</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Цена в книге, ₽</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Своё производство</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Правило в книге</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Петли</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Петля "Firmax Adevenced Plus" (с доводчиком)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>180</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Петли</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Петля "Firmax Adevenced Plus" (в угловой шкаф)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>350</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Петли</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Петля "Blum" (с доводчиком)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>450</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Петли</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Петля "Blum" (В угловой шкаф)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>590</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Подъёмники</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>газлифт</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>250</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Подъёмники</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aventos HF</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16085</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Подъёмники</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aventos HS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16569</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Подъёмники</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aventos HL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>17245</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Подъёмники</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aventos HK top</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8800</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Подъёмники</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Aventos HK top tipon</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10422</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Подъёмники</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Aventos HK XS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Подъёмники</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Aventos HK XS tipon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4704</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ручки и открывание</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Интегрировання ручка</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>900</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ручки и открывание</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tip on Boyard</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>350</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ручки и открывание</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tip on Blum</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>900</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Профиль Gola</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Gola Алюминий</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Профиль Gola</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Gola Черный</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Профиль Gola</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gola Белый</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Профиль Gola</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gola Золото</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ХДФ (задняя стенка)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ХДФ (серый, черный, белый)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>400</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Firmax скрытого монтажа</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Firmax скрытого монтажа от нажатия</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Alphaluх (метал/стекло)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2920</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Alphaluх (метал/стекло) от нажатия</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3910</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Скрытогомонтажа чс.выд Blum</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Скрытогомонтажа пол.выд Blum</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3955</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Скрытогомонтажа пол.выд tipon Blum</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6692</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Тандембокс antaro Blum</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7027</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Леграбокс Blum</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>9734</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Внут.Тандембокс antaro Blum</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>8798</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Внут.Леграбокс Blum</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12689</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Тандембокс antaro Blum tipon</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10345</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Леграбокс Blum tipon</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13326</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ящики и направляющие</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Подсветка для Alphaluх стеклянного ящика</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Сушки и корзины</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Сушка SU02/500</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2686</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Сушки и корзины</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Сушка SU02/600</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2928</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Сушки и корзины</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Сушка SU02/700</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3383</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Сушки и корзины</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Сушка SU02/800</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3808</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Сушки и корзины</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Сушка SU02/900</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>4234</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Сушки и корзины</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Выдвижная корзина-сушка MIRA KRS06/1/3/600</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>9600</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Сушки и корзины</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Выдвижная корзина-сушка MIRA KRS06/1/3/800</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11250</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Сушки и корзины</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Выдвижная корзина-сушка MIRA KRS06/1/3/900</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12150</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Бутылочницы (карго)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Boyard 150 KR08</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>4989</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Бутылочницы (карго)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Boyard 200 KR08</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>5855</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Бутылочницы (карго)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Boyard 300 KR19</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>8750</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Плинтус</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Плинтус низкий</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>500</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Плинтус</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Плинтус высокий</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>650</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Цоколь</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Цоколь 100мм</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>475</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Цоколь</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Цоколь 150мм</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>680</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Крепёж (крабы)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Комплект крабов</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>260</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/kp-calc/data/prices-draft.xlsx
+++ b/kp-calc/data/prices-draft.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -585,11 +585,11 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Прайс1 «ЛДСП_Кроношпан_Standart»</t>
+          <t>Прайс1, строка 87-135</t>
         </is>
       </c>
     </row>
@@ -611,11 +611,11 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Прайс1 «ЛДСП_Кроношпан_Color»</t>
+          <t>Прайс1, строка 138-177</t>
         </is>
       </c>
     </row>
@@ -637,23 +637,23 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Прайс1 «ЛДСП_Кроношпан_Contempo»</t>
+          <t>Прайс1, строка 180-214</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ЛДСП корпус</t>
+          <t>Фасады</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ЛДСП Кроношпан Trends</t>
+          <t>ЛДСП Egger (фасад)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -663,11 +663,11 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Прайс1 «ЛДСП_Кроношпан_Trends»</t>
+          <t>Прайс1 «ЛДСП_Egger»</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ЛДСП Egger (фасад)</t>
+          <t>Ботаника МДФ 16, обратная белая</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -687,13 +687,17 @@
           <t>м²</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>E×0,8</t>
+        </is>
+      </c>
       <c r="E7" t="n">
-        <v>144</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Прайс1 «ЛДСП_Egger»</t>
+          <t>Прайс1 «Ботаника_мдф16_обр_белая»</t>
         </is>
       </c>
     </row>
@@ -705,7 +709,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ботаника МДФ 16, обратная белая</t>
+          <t>Ботаника МДФ 16, обратная в цвет</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -719,11 +723,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_мдф16_обр_белая»</t>
+          <t>Прайс1 «Ботаника_мдф16_обр_в_цвет»</t>
         </is>
       </c>
     </row>
@@ -735,7 +739,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ботаника МДФ 16, обратная в цвет</t>
+          <t>Ботаника ДСП 16, обратная белая</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -743,17 +747,13 @@
           <t>м²</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>E×0,8</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_мдф16_обр_в_цвет»</t>
+          <t>Прайс1 «Ботаника_дсп16_обр_белая»</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ботаника ДСП 16, обратная белая</t>
+          <t>Ботаника ДСП 16, обратная в цвет</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_дсп16_обр_белая»</t>
+          <t>Прайс1 «Ботаника_дсп16_обр_в_цвет»</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ботаника ДСП 16, обратная в цвет</t>
+          <t>Egger Perfect Sense TOP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,11 +801,11 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_дсп16_обр_в_цвет»</t>
+          <t>Прайс1 «Perfect_sence_TOP_Egger»</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Egger Perfect Sense TOP</t>
+          <t>Egger Perfect Sense Smart</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Прайс1 «Perfect_sence_TOP_Egger»</t>
+          <t>Прайс1 «Perfect_sence_Smart_Egger»</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Egger Perfect Sense Smart</t>
+          <t>Egger Perfect Sense</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -853,11 +853,11 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Прайс1 «Perfect_sence_Smart_Egger»</t>
+          <t>Прайс1 «Perfect_sence_Egger»</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Egger Perfect Sense</t>
+          <t>Эмаль матовая</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -879,11 +879,11 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Прайс1 «Perfect_sence_Egger»</t>
+          <t>Прайс1, строка 1296</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Эмаль матовая</t>
+          <t>Эмаль глянец</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Прайс1, строка 1296</t>
+          <t>Прайс1, строка 1297</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Эмаль глянец</t>
+          <t>Эмаль фрезеровка</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Прайс1, строка 1297</t>
+          <t>Прайс1, строка 1298</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Эмаль фрезеровка</t>
+          <t>Эмаль фрезеровка с патиной</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Прайс1, строка 1298</t>
+          <t>Прайс1, строка 1299</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Эмаль фрезеровка с патиной</t>
+          <t>ALVIC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -983,11 +983,11 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Прайс1, строка 1299</t>
+          <t>Прайс1 «ALVIC»</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ALVIC</t>
+          <t>AGT односторонний</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1009,11 +1009,11 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Прайс1 «ALVIC»</t>
+          <t>Прайс1 «AGT_односторонний»</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AGT односторонний</t>
+          <t>AGT Supramat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1035,11 +1035,11 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Прайс1 «AGT_односторонний»</t>
+          <t>Прайс1 «AGT_supramat»</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AGT Supramat</t>
+          <t>Fenix</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1061,11 +1061,11 @@
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Прайс1 «AGT_supramat»</t>
+          <t>Прайс1 «Fenix»</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fenix</t>
+          <t>ПВХ Дядя Фёдор</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1087,11 +1087,11 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Прайс1 «Fenix»</t>
+          <t>Прайс1 «ПВХ_ДядяФедор»</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ПВХ Дядя Фёдор</t>
+          <t>Шпон</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1113,11 +1113,11 @@
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Прайс1 «ПВХ_ДядяФедор»</t>
+          <t>Прайс1 «Шпон»</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Шпон</t>
+          <t>Массив</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1139,11 +1139,11 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Прайс1 «Шпон»</t>
+          <t>Прайс1 «Массив»</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Массив</t>
+          <t>Стекло в алюминиевой рамке</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1165,37 +1165,41 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Прайс1 «Массив»</t>
+          <t>Прайс1 «Стекло_в_Ал_Рамке»</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Фасады</t>
+          <t>Столешницы</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Стекло в алюминиевой рамке</t>
+          <t>Ботаника ДСП 38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>м.п.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>E×0,6</t>
+        </is>
+      </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Прайс1 «Стекло_в_Ал_Рамке»</t>
+          <t>Прайс1 «Ботаника_ДСП38»</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1211,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ботаника ДСП 38</t>
+          <t>Ботаника ФНР 38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1225,7 +1229,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_ДСП38»</t>
+          <t>Прайс1 «Ботаника_ФНР38»</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1241,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ботаника ФНР 38</t>
+          <t>Ботаника ФНР 18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1255,7 +1259,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_ФНР38»</t>
+          <t>Прайс1 «Ботаника_ФНР18»</t>
         </is>
       </c>
     </row>
@@ -1267,25 +1271,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ботаника ФНР 18</t>
+          <t>Угловой сегмент Ботаника ДСП 38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>м.п.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>E×0,6</t>
-        </is>
-      </c>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Прайс1 «Ботаника_ФНР18»</t>
+          <t>Прайс1 «Угловой_сегмент_Ботаника_ДСП38»</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Угловой сегмент Ботаника ДСП 38</t>
+          <t>Угловой сегмент Ботаника ФНР 38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Прайс1 «Угловой_сегмент_Ботаника_ДСП38»</t>
+          <t>Прайс1 «Угловой_сегмент_Ботаника_ФНР38»</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Угловой сегмент Ботаника ФНР 38</t>
+          <t>Угловой сегмент Ботаника ФНР 18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1337,19 +1337,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Прайс1 «Угловой_сегмент_Ботаника_ФНР38»</t>
+          <t>Прайс1, строка 2143-2147</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Столешницы</t>
+          <t>Стеновые панели</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Угловой сегмент Ботаника ФНР 18</t>
+          <t>Ботаника ДСП стеновая (панель 600 или 1200 × 3000/4150)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1357,69 +1357,73 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>E×0,6</t>
+        </is>
+      </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Прайс1, строка 2143-2147</t>
+          <t>Прайс1 «Стеновая_Ботаника_ДСП»</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Стеновые панели</t>
+          <t>Плинтус</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ботаника ДСП стеновая (панель 600 или 1200 × 3000/4150)</t>
+          <t>Плинтус</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>E×0,6</t>
-        </is>
-      </c>
+          <t>шт (3 м)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Прайс1 «Стеновая_Ботаника_ДСП»</t>
+          <t>Прайс1 «Плинтус_3м_шт»</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Плинтус</t>
+          <t>Фурнитура</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Плинтус</t>
+          <t>Петли</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>шт (3 м)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
       <c r="E34" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Прайс1 «Плинтус_3м_шт»</t>
+          <t>Прайс Фурнитура «Петли»</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1435,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Петли</t>
+          <t>Подъёмники</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1445,11 +1449,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Петли»</t>
+          <t>Прайс Фурнитура «Подъемный_механизм»</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1465,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Подъёмники</t>
+          <t>Ручки и открывание</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1475,11 +1479,11 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Подъемный_механизм»</t>
+          <t>Прайс Фурнитура «Ручка_верх»</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1495,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ручки и открывание</t>
+          <t>Профиль Gola</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1505,11 +1509,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Ручка_верх»</t>
+          <t>Прайс Фурнитура «Профиль_GOLA_G13»</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1525,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Профиль Gola</t>
+          <t>ХДФ (задняя стенка)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1535,11 +1539,11 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Профиль_GOLA_G13»</t>
+          <t>Прайс Фурнитура «ХДФ»</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1555,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ХДФ (задняя стенка)</t>
+          <t>Ящики и направляющие</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1565,11 +1569,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «ХДФ»</t>
+          <t>Прайс Фурнитура «Выкатной_механизм»</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1585,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ящики и направляющие</t>
+          <t>Сушки и корзины</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1595,11 +1599,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Выкатной_механизм»</t>
+          <t>Прайс Фурнитура «Сушка»</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1615,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Сушки и корзины</t>
+          <t>Бутылочницы (карго)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1625,11 +1629,11 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Сушка»</t>
+          <t>Прайс Фурнитура «Бутылочница»</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1645,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Бутылочницы (карго)</t>
+          <t>Плинтус</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1655,11 +1659,11 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Бутылочница»</t>
+          <t>Прайс Фурнитура «Плинтус»</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1675,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Плинтус</t>
+          <t>Цоколь</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1689,7 +1693,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Плинтус»</t>
+          <t>Прайс Фурнитура «Цоколь_прайс»</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1705,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Цоколь</t>
+          <t>Крепёж (крабы)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1715,41 +1719,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Цоколь_прайс»</t>
+          <t>Прайс Фурнитура «Комплект_крабов»</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Фурнитура</t>
+          <t>Подсветка</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Крепёж (крабы)</t>
+          <t>Лента 24 В, 4000 K (одна позиция)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м.п.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>закупка</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>1</v>
+          <t>вручную</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Прайс Фурнитура «Комплект_крабов»</t>
+          <t>решение владельца 27.10.2026</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1767,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Лента 24 В, 4000 K (одна позиция)</t>
+          <t>Профиль врезной / накладной</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1781,7 +1787,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>решение владельца 27.10.2026</t>
+          <t>паз включён в цену профиля</t>
         </is>
       </c>
     </row>
@@ -1793,17 +1799,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Профиль врезной / накладной</t>
+          <t>Блоки питания 24 В</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>м.п.</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>вручную</t>
+          <t>подбор по мощности</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1813,7 +1819,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>паз включён в цену профиля</t>
+          <t>цены дать</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1831,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Блоки питания 24 В</t>
+          <t>Выключатели: кнопка, сенсор на взмах, датчик двери</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1835,7 +1841,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>подбор по мощности</t>
+          <t>вручную</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1844,38 +1850,6 @@
         </is>
       </c>
       <c r="F48" t="inlineStr">
-        <is>
-          <t>цены дать</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Подсветка</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Выключатели: кнопка, сенсор на взмах, датчик двери</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>вручную</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
         <is>
           <t>цены дать</t>
         </is>
@@ -1892,7 +1866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5989,7 +5963,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Орех 517 Т 2750*1830 РЛ</t>
+          <t>Береза Снежная 1715 BS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5998,15 +5972,12 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E146" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H146">
         <f>IF(D146="","",ROUND(D146/IF(G146="",5.796,G146)*1.2+150,0))</f>
         <v/>
@@ -6020,7 +5991,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Орех 519 Т 2750*1830 РЛ</t>
+          <t>Бук Бавария 381 PR</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6029,15 +6000,12 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E147" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H147">
         <f>IF(D147="","",ROUND(D147/IF(G147="",5.796,G147)*1.2+150,0))</f>
         <v/>
@@ -6051,7 +6019,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Орех 592 Т 2750*1830 РЛ</t>
+          <t>Венге 854 PR/BS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6060,15 +6028,12 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E148" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H148">
         <f>IF(D148="","",ROUND(D148/IF(G148="",5.796,G148)*1.2+150,0))</f>
         <v/>
@@ -6082,7 +6047,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Орех Пегасо 531 Т 2750*1830 РЛ</t>
+          <t>Венге Луизиана 9763 BS</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6091,15 +6056,12 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E149" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H149">
         <f>IF(D149="","",ROUND(D149/IF(G149="",5.796,G149)*1.2+150,0))</f>
         <v/>
@@ -6113,7 +6075,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Светло-серая 771 Ш 2750*1830 РЛ</t>
+          <t>Венге Подлинный  9016 BS</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -6122,15 +6084,12 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E150" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H150">
         <f>IF(D150="","",ROUND(D150/IF(G150="",5.796,G150)*1.2+150,0))</f>
         <v/>
@@ -6144,7 +6103,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Сильвер 882 Ш 2750*1830 РЛ</t>
+          <t>Венге Цаво 3354 PR</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -6153,15 +6112,12 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E151" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H151">
         <f>IF(D151="","",ROUND(D151/IF(G151="",5.796,G151)*1.2+150,0))</f>
         <v/>
@@ -6175,7 +6131,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ясень Анкор 238Л 2750*1830 РЛ</t>
+          <t>Вишня Oксфорд 088 PR</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6184,15 +6140,12 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E152" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H152">
         <f>IF(D152="","",ROUND(D152/IF(G152="",5.796,G152)*1.2+150,0))</f>
         <v/>
@@ -6206,7 +6159,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ясень Анкор 239Л 2750*1830 РЛ</t>
+          <t>Вишня Риверсайд Светлая  К077 PW</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6215,15 +6168,12 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E153" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H153">
         <f>IF(D153="","",ROUND(D153/IF(G153="",5.796,G153)*1.2+150,0))</f>
         <v/>
@@ -6237,7 +6187,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ясень Шимо 243Т 2750*1830 РЛ</t>
+          <t>Вишня Риверсайд Темная К078 PW</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6246,15 +6196,12 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E154" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H154">
         <f>IF(D154="","",ROUND(D154/IF(G154="",5.796,G154)*1.2+150,0))</f>
         <v/>
@@ -6268,7 +6215,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ясень Шимо 245Т 2750*1830 РЛ</t>
+          <t>Вяз Либерти Светлый К017 PW</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6277,15 +6224,12 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E155" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H155">
         <f>IF(D155="","",ROUND(D155/IF(G155="",5.796,G155)*1.2+150,0))</f>
         <v/>
@@ -6299,7 +6243,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Арабеска 181 Л 2750*1830 РЛ</t>
+          <t>Вяз Либерти Дымчатый  К018 PW</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6308,15 +6252,12 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E156" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H156">
         <f>IF(D156="","",ROUND(D156/IF(G156="",5.796,G156)*1.2+150,0))</f>
         <v/>
@@ -6330,7 +6271,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Аризона 192 Т 2750*1830 РЛ</t>
+          <t>Вяз Либерти Серебряный  К019 PW</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6339,15 +6280,12 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E157" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H157">
         <f>IF(D157="","",ROUND(D157/IF(G157="",5.796,G157)*1.2+150,0))</f>
         <v/>
@@ -6361,7 +6299,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Беж-Камео 712Ш 2750*1830 РЛ</t>
+          <t>Вяз Натуральный Благородный 5500 SU</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6370,15 +6308,12 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E158" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H158">
         <f>IF(D158="","",ROUND(D158/IF(G158="",5.796,G158)*1.2+150,0))</f>
         <v/>
@@ -6392,7 +6327,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Беж-латте 711Ш 2750*1830 РЛ</t>
+          <t>Дуб Белый Craft K001 PW</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6401,15 +6336,12 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E159" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H159">
         <f>IF(D159="","",ROUND(D159/IF(G159="",5.796,G159)*1.2+150,0))</f>
         <v/>
@@ -6423,7 +6355,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Бежевая 714Ш 2750*1830 РЛ</t>
+          <t>Дуб Винтаж Оксид  5194 SN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6432,15 +6364,12 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2300</v>
+        <v>3509</v>
       </c>
       <c r="E160" t="n">
-        <v>1522.1</v>
+        <v>2132.97</v>
       </c>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H160">
         <f>IF(D160="","",ROUND(D160/IF(G160="",5.796,G160)*1.2+150,0))</f>
         <v/>
@@ -6454,7 +6383,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Береза Белая 116ШП 2750*1830 РЛ</t>
+          <t>Дуб Венге  6495 BS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6463,15 +6392,12 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E161" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H161">
         <f>IF(D161="","",ROUND(D161/IF(G161="",5.796,G161)*1.2+150,0))</f>
         <v/>
@@ -6485,7 +6411,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Вишня Скандинавкая 320Т 2750*1830 РЛ</t>
+          <t>Дуб Горный светлый 740 PR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6494,15 +6420,12 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E162" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H162">
         <f>IF(D162="","",ROUND(D162/IF(G162="",5.796,G162)*1.2+150,0))</f>
         <v/>
@@ -6516,7 +6439,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Грей 775 Ш 2750*1830 РЛ</t>
+          <t>Дуб Золотой Craft K003 PW</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6525,15 +6448,12 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E163" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F163" t="inlineStr"/>
-      <c r="G163" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H163">
         <f>IF(D163="","",ROUND(D163/IF(G163="",5.796,G163)*1.2+150,0))</f>
         <v/>
@@ -6547,7 +6467,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Дуб 131 ШП 2750*1830 РЛ</t>
+          <t>Дуб Кофейный Urban K007 PW</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6556,15 +6476,12 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E164" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F164" t="inlineStr"/>
-      <c r="G164" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H164">
         <f>IF(D164="","",ROUND(D164/IF(G164="",5.796,G164)*1.2+150,0))</f>
         <v/>
@@ -6578,7 +6495,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Дуб 133 ШП 2750*1830 РЛ</t>
+          <t>Дуб Лисса 8925 BS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6587,15 +6504,12 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2300</v>
+        <v>3322</v>
       </c>
       <c r="E165" t="n">
-        <v>1522.1</v>
+        <v>2038.48</v>
       </c>
       <c r="F165" t="inlineStr"/>
-      <c r="G165" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H165">
         <f>IF(D165="","",ROUND(D165/IF(G165="",5.796,G165)*1.2+150,0))</f>
         <v/>
@@ -6609,7 +6523,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Дуб Антик 103 Л 2750*1830 РЛ</t>
+          <t>Дуб Молочный 8622 PR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6618,15 +6532,12 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E166" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H166">
         <f>IF(D166="","",ROUND(D166/IF(G166="",5.796,G166)*1.2+150,0))</f>
         <v/>
@@ -6640,7 +6551,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Дуб Аррива 159 Л 2750*1830 РЛ</t>
+          <t>Дуб Нагано 8431 SN</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6649,15 +6560,12 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E167" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F167" t="inlineStr"/>
-      <c r="G167" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H167">
         <f>IF(D167="","",ROUND(D167/IF(G167="",5.796,G167)*1.2+150,0))</f>
         <v/>
@@ -6671,7 +6579,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Дуб Бунратти 190ТС 2750*1830 РЛ</t>
+          <t>Дуб Сонома Светлый  3025 SN</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6680,15 +6588,12 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E168" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F168" t="inlineStr"/>
-      <c r="G168" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H168">
         <f>IF(D168="","",ROUND(D168/IF(G168="",5.796,G168)*1.2+150,0))</f>
         <v/>
@@ -6702,7 +6607,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Дуб Кантри 112 Л 2750*1830 РЛ</t>
+          <t>Дуб Серый Craft K002 PW</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6711,15 +6616,12 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E169" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H169">
         <f>IF(D169="","",ROUND(D169/IF(G169="",5.796,G169)*1.2+150,0))</f>
         <v/>
@@ -6733,7 +6635,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Дуб Русский111 Л 2750*1830 РЛ</t>
+          <t>Дуб Табачный Craft K004 PW</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6742,15 +6644,12 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E170" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H170">
         <f>IF(D170="","",ROUND(D170/IF(G170="",5.796,G170)*1.2+150,0))</f>
         <v/>
@@ -6764,7 +6663,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Дуб Сафари 158 Л 2750*1830 РЛ</t>
+          <t>Дуб Устричный Urban K005 PW</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6773,15 +6672,12 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E171" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F171" t="inlineStr"/>
-      <c r="G171" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H171">
         <f>IF(D171="","",ROUND(D171/IF(G171="",5.796,G171)*1.2+150,0))</f>
         <v/>
@@ -6795,7 +6691,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Дуб Седан 134 Т 2750*1830 РЛ</t>
+          <t>Дуб Феррара 8921 PR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6804,15 +6700,12 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E172" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H172">
         <f>IF(D172="","",ROUND(D172/IF(G172="",5.796,G172)*1.2+150,0))</f>
         <v/>
@@ -6826,7 +6719,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Дуб Скальный 145 Л 2750*1830 РЛ</t>
+          <t>Дуб Экспрессив Бронзовый  K090 PW</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6835,15 +6728,12 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E173" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H173">
         <f>IF(D173="","",ROUND(D173/IF(G173="",5.796,G173)*1.2+150,0))</f>
         <v/>
@@ -6857,7 +6747,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Дуб Тортона 104 Т 2750*1830 РЛ</t>
+          <t>Дуб Экспрессив Песочный  K076 PW</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6866,15 +6756,12 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E174" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H174">
         <f>IF(D174="","",ROUND(D174/IF(G174="",5.796,G174)*1.2+150,0))</f>
         <v/>
@@ -6888,7 +6775,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Дуб Шато 110 Т 2750*1830 РЛ</t>
+          <t>Дуб Янтарный Urban K006 PW</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6897,15 +6784,12 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E175" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H175">
         <f>IF(D175="","",ROUND(D175/IF(G175="",5.796,G175)*1.2+150,0))</f>
         <v/>
@@ -6919,7 +6803,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Дуб Ясный 127 Т 2750*1830 РЛ</t>
+          <t>Клен 375 PR</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6928,15 +6812,12 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E176" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F176" t="inlineStr"/>
-      <c r="G176" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H176">
         <f>IF(D176="","",ROUND(D176/IF(G176="",5.796,G176)*1.2+150,0))</f>
         <v/>
@@ -6950,7 +6831,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Желтая 730 Ш 2750*1830 РЛ</t>
+          <t>Коко Бола 8995 BS</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6959,15 +6840,12 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>2300</v>
+        <v>3322</v>
       </c>
       <c r="E177" t="n">
-        <v>1522.1</v>
+        <v>2038.48</v>
       </c>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H177">
         <f>IF(D177="","",ROUND(D177/IF(G177="",5.796,G177)*1.2+150,0))</f>
         <v/>
@@ -6981,7 +6859,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Зеленая 764 Ш 2750*1830 РЛ</t>
+          <t>Морское Дерево Винтаж K015 PW</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6990,15 +6868,12 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E178" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H178">
         <f>IF(D178="","",ROUND(D178/IF(G178="",5.796,G178)*1.2+150,0))</f>
         <v/>
@@ -7012,7 +6887,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Зеленая Степная 763 Ш 2750*1830 РЛ</t>
+          <t>Морское Дерево Карбон K016 PW</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -7021,15 +6896,12 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E179" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H179">
         <f>IF(D179="","",ROUND(D179/IF(G179="",5.796,G179)*1.2+150,0))</f>
         <v/>
@@ -7043,7 +6915,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Красная 740 Ш 2750*1830 РЛ</t>
+          <t>Ольха горская 1912 PR</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7052,15 +6924,12 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E180" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H180">
         <f>IF(D180="","",ROUND(D180/IF(G180="",5.796,G180)*1.2+150,0))</f>
         <v/>
@@ -7074,7 +6943,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Лаванда 721 ТС 2750*1830 РЛ</t>
+          <t>Орех 729 PR</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7083,15 +6952,12 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E181" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H181">
         <f>IF(D181="","",ROUND(D181/IF(G181="",5.796,G181)*1.2+150,0))</f>
         <v/>
@@ -7105,7 +6971,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Лиственница 212ШП 2750*1830 РЛ</t>
+          <t>Ночи Гварнери  9455 PR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7114,15 +6980,12 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>2300</v>
+        <v>3344</v>
       </c>
       <c r="E182" t="n">
-        <v>1522.1</v>
+        <v>2049.6</v>
       </c>
       <c r="F182" t="inlineStr"/>
-      <c r="G182" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H182">
         <f>IF(D182="","",ROUND(D182/IF(G182="",5.796,G182)*1.2+150,0))</f>
         <v/>
@@ -7136,7 +6999,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Лиственница 214 ШП 2750*1830 РЛ</t>
+          <t>Орех Каминный Select 020 PW</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7145,15 +7008,12 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E183" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H183">
         <f>IF(D183="","",ROUND(D183/IF(G183="",5.796,G183)*1.2+150,0))</f>
         <v/>
@@ -7167,7 +7027,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Мистик 726Ш 2750*1830 РЛ</t>
+          <t>Орех Опера 481 BS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -7176,15 +7036,12 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E184" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H184">
         <f>IF(D184="","",ROUND(D184/IF(G184="",5.796,G184)*1.2+150,0))</f>
         <v/>
@@ -7198,7 +7055,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Мокка 716Ш 2750*1830 РЛ</t>
+          <t>Орех Лион Светлый 9614 BS</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -7207,15 +7064,12 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2300</v>
+        <v>3344</v>
       </c>
       <c r="E185" t="n">
-        <v>1522.1</v>
+        <v>2049.6</v>
       </c>
       <c r="F185" t="inlineStr"/>
-      <c r="G185" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H185">
         <f>IF(D185="","",ROUND(D185/IF(G185="",5.796,G185)*1.2+150,0))</f>
         <v/>
@@ -7229,7 +7083,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Моринга 210 Л 2750*1830 РЛ</t>
+          <t>Орех Мария Луиза (Итальянский) 9490 PR</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -7238,15 +7092,12 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E186" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H186">
         <f>IF(D186="","",ROUND(D186/IF(G186="",5.796,G186)*1.2+150,0))</f>
         <v/>
@@ -7260,7 +7111,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Мята 766 ТС 2750*1830 РЛ</t>
+          <t>Орех Светлый Select K008 PW</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7269,15 +7120,12 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E187" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H187">
         <f>IF(D187="","",ROUND(D187/IF(G187="",5.796,G187)*1.2+150,0))</f>
         <v/>
@@ -7291,7 +7139,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Небесно-голубая 720 Ш 2750*1830 РЛ</t>
+          <t>Орех Темный Select K009 PW</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7300,15 +7148,12 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E188" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F188" t="inlineStr"/>
-      <c r="G188" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H188">
         <f>IF(D188="","",ROUND(D188/IF(G188="",5.796,G188)*1.2+150,0))</f>
         <v/>
@@ -7322,7 +7167,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Оранжевая 735 Ш 2750*1830 РЛ</t>
+          <t>Орех Тьеполо 8953 SU</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7331,15 +7176,12 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>2300</v>
+        <v>3344</v>
       </c>
       <c r="E189" t="n">
-        <v>1522.1</v>
+        <v>2049.6</v>
       </c>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H189">
         <f>IF(D189="","",ROUND(D189/IF(G189="",5.796,G189)*1.2+150,0))</f>
         <v/>
@@ -7353,7 +7195,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Орех Милано 534 Т 2750*1830 РЛ</t>
+          <t>Ночи Экко 9459 PR</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7362,15 +7204,12 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E190" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H190">
         <f>IF(D190="","",ROUND(D190/IF(G190="",5.796,G190)*1.2+150,0))</f>
         <v/>
@@ -7384,7 +7223,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Орех Миланский 500 Т 2750*1830 РЛ</t>
+          <t>Яблоня Локарно 1972 BS</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7393,15 +7232,12 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E191" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F191" t="inlineStr"/>
-      <c r="G191" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H191">
         <f>IF(D191="","",ROUND(D191/IF(G191="",5.796,G191)*1.2+150,0))</f>
         <v/>
@@ -7415,7 +7251,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Песочный 0515 РЕ</t>
+          <t>Ясень Таормина 8503 BS</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7424,10 +7260,10 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2300</v>
+        <v>3344</v>
       </c>
       <c r="E192" t="n">
-        <v>1522.1</v>
+        <v>2049.6</v>
       </c>
       <c r="F192" t="inlineStr"/>
       <c r="H192">
@@ -7438,12 +7274,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ЛДСП Кроношпан Color</t>
+          <t>ЛДСП Кроношпан Standart</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Сосна Ларедо 230ШП 2750*1830 РЛ</t>
+          <t>Ясень Шимо Светлый  3356 BS</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7452,15 +7288,12 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E193" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F193" t="inlineStr"/>
-      <c r="G193" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H193">
         <f>IF(D193="","",ROUND(D193/IF(G193="",5.796,G193)*1.2+150,0))</f>
         <v/>
@@ -7469,12 +7302,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ЛДСП Кроношпан Color</t>
+          <t>ЛДСП Кроношпан Standart</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Сосна Нордик 231 Л 2750*1830 РЛ</t>
+          <t>Ясень Шимо Темный 3357 PR</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7483,15 +7316,12 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>2300</v>
+        <v>3267</v>
       </c>
       <c r="E194" t="n">
-        <v>1522.1</v>
+        <v>2010.69</v>
       </c>
       <c r="F194" t="inlineStr"/>
-      <c r="G194" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H194">
         <f>IF(D194="","",ROUND(D194/IF(G194="",5.796,G194)*1.2+150,0))</f>
         <v/>
@@ -7505,7 +7335,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Сосна Прованс 234 Л 2750*1830 РЛ</t>
+          <t>Белый (Влагостойкая ДСП) 101 SM</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7514,15 +7344,12 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>2300</v>
+        <v>3729</v>
       </c>
       <c r="E195" t="n">
-        <v>1522.1</v>
+        <v>2244.13</v>
       </c>
       <c r="F195" t="inlineStr"/>
-      <c r="G195" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H195">
         <f>IF(D195="","",ROUND(D195/IF(G195="",5.796,G195)*1.2+150,0))</f>
         <v/>
@@ -7536,7 +7363,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Сосно Пике 228 ШП 2750*1830 РЛ</t>
+          <t>Алюминий 881 PE</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7545,15 +7372,12 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2300</v>
+        <v>3344</v>
       </c>
       <c r="E196" t="n">
-        <v>1522.1</v>
+        <v>2049.6</v>
       </c>
       <c r="F196" t="inlineStr"/>
-      <c r="G196" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H196">
         <f>IF(D196="","",ROUND(D196/IF(G196="",5.796,G196)*1.2+150,0))</f>
         <v/>
@@ -7567,7 +7391,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Таксония 171 Т 2750*1830 РЛ</t>
+          <t>Антрацит  164 PE</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7576,15 +7400,12 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E197" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F197" t="inlineStr"/>
-      <c r="G197" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H197">
         <f>IF(D197="","",ROUND(D197/IF(G197="",5.796,G197)*1.2+150,0))</f>
         <v/>
@@ -7598,7 +7419,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Твигги 816 ТС 2750*1830 РЛ</t>
+          <t>Бежевый 522 PE</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7607,15 +7428,12 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>2300</v>
+        <v>3289</v>
       </c>
       <c r="E198" t="n">
-        <v>1522.1</v>
+        <v>2021.81</v>
       </c>
       <c r="F198" t="inlineStr"/>
-      <c r="G198" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H198">
         <f>IF(D198="","",ROUND(D198/IF(G198="",5.796,G198)*1.2+150,0))</f>
         <v/>
@@ -7629,7 +7447,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Твист 811 ТС 2750*1830 РЛ</t>
+          <t>Белый Бриллиант 8681 SM</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7638,15 +7456,12 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>2300</v>
+        <v>3608</v>
       </c>
       <c r="E199" t="n">
-        <v>1522.1</v>
+        <v>2182.99</v>
       </c>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H199">
         <f>IF(D199="","",ROUND(D199/IF(G199="",5.796,G199)*1.2+150,0))</f>
         <v/>
@@ -7660,7 +7475,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Титан 883 Ш 2750*1830 РЛ</t>
+          <t>Белый Снег 8685 SN</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7669,15 +7484,12 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>2300</v>
+        <v>3729</v>
       </c>
       <c r="E200" t="n">
-        <v>1522.1</v>
+        <v>2244.13</v>
       </c>
       <c r="F200" t="inlineStr"/>
-      <c r="G200" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H200">
         <f>IF(D200="","",ROUND(D200/IF(G200="",5.796,G200)*1.2+150,0))</f>
         <v/>
@@ -7691,7 +7503,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Трансильвания 166 ТС 2750*1830 РЛ</t>
+          <t>Белый Снег 8685 SM</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7700,15 +7512,12 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2300</v>
+        <v>3663</v>
       </c>
       <c r="E201" t="n">
-        <v>1522.1</v>
+        <v>2210.78</v>
       </c>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H201">
         <f>IF(D201="","",ROUND(D201/IF(G201="",5.796,G201)*1.2+150,0))</f>
         <v/>
@@ -7722,7 +7531,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Черная 799 Ш 2750*1830 РЛ</t>
+          <t>Белый Фасадный 101 SM/РЕ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7731,15 +7540,12 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>2300</v>
+        <v>3531</v>
       </c>
       <c r="E202" t="n">
-        <v>1522.1</v>
+        <v>2144.08</v>
       </c>
       <c r="F202" t="inlineStr"/>
-      <c r="G202" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H202">
         <f>IF(D202="","",ROUND(D202/IF(G202="",5.796,G202)*1.2+150,0))</f>
         <v/>
@@ -7753,7 +7559,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Эбони Светлый 165 ШП 2750*1830 РЛ</t>
+          <t>Ваниль 9569 PE</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7762,15 +7568,12 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>2300</v>
+        <v>3300</v>
       </c>
       <c r="E203" t="n">
-        <v>1522.1</v>
+        <v>2027.37</v>
       </c>
       <c r="F203" t="inlineStr"/>
-      <c r="G203" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H203">
         <f>IF(D203="","",ROUND(D203/IF(G203="",5.796,G203)*1.2+150,0))</f>
         <v/>
@@ -7784,7 +7587,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Эвкалипт Мистери 168 Л 2750*1830 РЛ</t>
+          <t>Зеленая Мамба  7190 BS</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7793,15 +7596,12 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>2300</v>
+        <v>3630</v>
       </c>
       <c r="E204" t="n">
-        <v>1522.1</v>
+        <v>2194.11</v>
       </c>
       <c r="F204" t="inlineStr"/>
-      <c r="G204" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H204">
         <f>IF(D204="","",ROUND(D204/IF(G204="",5.796,G204)*1.2+150,0))</f>
         <v/>
@@ -7815,7 +7615,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ясень Валенсия 241 Т 2750*1830 РЛ</t>
+          <t>Зеленый Лайм 5519 BS</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7824,15 +7624,12 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>2300</v>
+        <v>3630</v>
       </c>
       <c r="E205" t="n">
-        <v>1522.1</v>
+        <v>2194.11</v>
       </c>
       <c r="F205" t="inlineStr"/>
-      <c r="G205" t="n">
-        <v>5.032</v>
-      </c>
       <c r="H205">
         <f>IF(D205="","",ROUND(D205/IF(G205="",5.796,G205)*1.2+150,0))</f>
         <v/>
@@ -7846,7 +7643,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Береза Снежная 1715 BS</t>
+          <t>Капучино  0301 SU</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7855,10 +7652,10 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>3267</v>
+        <v>3630</v>
       </c>
       <c r="E206" t="n">
-        <v>2010.69</v>
+        <v>2194.11</v>
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="H206">
@@ -7874,7 +7671,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Бук Бавария 381 PR</t>
+          <t>Кашемир 5981 BS</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7883,10 +7680,10 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>3267</v>
+        <v>3289</v>
       </c>
       <c r="E207" t="n">
-        <v>2010.69</v>
+        <v>2021.81</v>
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="H207">
@@ -7902,7 +7699,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Венге 854 PR/BS</t>
+          <t>Капри Синий (Голубой) 121 BS</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7911,10 +7708,10 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>3267</v>
+        <v>3344</v>
       </c>
       <c r="E208" t="n">
-        <v>2010.69</v>
+        <v>2049.6</v>
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="H208">
@@ -7930,7 +7727,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Венге Луизиана 9763 BS</t>
+          <t>Королевский Синий 125 BS</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7939,10 +7736,10 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>3289</v>
+        <v>3344</v>
       </c>
       <c r="E209" t="n">
-        <v>2021.81</v>
+        <v>2049.6</v>
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="H209">
@@ -7958,7 +7755,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Венге Подлинный  9016 BS</t>
+          <t>Керамический Красный  К098 SU</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7967,10 +7764,10 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>3289</v>
+        <v>3630</v>
       </c>
       <c r="E210" t="n">
-        <v>2021.81</v>
+        <v>2194.11</v>
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="H210">
@@ -7986,7 +7783,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Венге Цаво 3354 PR</t>
+          <t>Кобальт Серый  6299 BS</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7995,10 +7792,10 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>3267</v>
+        <v>3630</v>
       </c>
       <c r="E211" t="n">
-        <v>2010.69</v>
+        <v>2194.11</v>
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="H211">
@@ -8014,7 +7811,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Вишня Oксфорд 088 PR</t>
+          <t>Красный 149 BS</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8023,10 +7820,10 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>3267</v>
+        <v>3344</v>
       </c>
       <c r="E212" t="n">
-        <v>2010.69</v>
+        <v>2049.6</v>
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="H212">
@@ -8042,7 +7839,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Вишня Риверсайд Светлая  К077 PW</t>
+          <t>Красный Чили 7113 BS</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -8051,10 +7848,10 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>3289</v>
+        <v>3630</v>
       </c>
       <c r="E213" t="n">
-        <v>2021.81</v>
+        <v>2194.11</v>
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="H213">
@@ -8070,7 +7867,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Вишня Риверсайд Темная К078 PW</t>
+          <t>Красный Оксид  9551 PE</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -8079,10 +7876,10 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>3289</v>
+        <v>3344</v>
       </c>
       <c r="E214" t="n">
-        <v>2021.81</v>
+        <v>2049.6</v>
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="H214">
@@ -8098,7 +7895,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Вяз Либерти Светлый К017 PW</t>
+          <t>Кремовый 7031 PE</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8107,10 +7904,10 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>3289</v>
+        <v>3300</v>
       </c>
       <c r="E215" t="n">
-        <v>2021.81</v>
+        <v>2027.37</v>
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="H215">
@@ -8126,7 +7923,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Вяз Либерти Дымчатый  К018 PW</t>
+          <t>Лаванда 8536 BS</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -8135,10 +7932,10 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>3289</v>
+        <v>3630</v>
       </c>
       <c r="E216" t="n">
-        <v>2021.81</v>
+        <v>2194.11</v>
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="H216">
@@ -8154,7 +7951,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Вяз Либерти Серебряный  К019 PW</t>
+          <t>Лате(Темный) 7166 BS</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8163,10 +7960,10 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>3289</v>
+        <v>3630</v>
       </c>
       <c r="E217" t="n">
-        <v>2021.81</v>
+        <v>2194.11</v>
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="H217">
@@ -8182,7 +7979,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Вяз Натуральный Благородный 5500 SU</t>
+          <t>Лимонный Сорбет 7123 BS</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -8191,10 +7988,10 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>3289</v>
+        <v>3344</v>
       </c>
       <c r="E218" t="n">
-        <v>2021.81</v>
+        <v>2049.6</v>
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="H218">
@@ -8210,7 +8007,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Дуб Белый Craft K001 PW</t>
+          <t>Макиато (Лате) 8533 BS</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8219,10 +8016,10 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>3289</v>
+        <v>3344</v>
       </c>
       <c r="E219" t="n">
-        <v>2021.81</v>
+        <v>2049.6</v>
       </c>
       <c r="F219" t="inlineStr"/>
       <c r="H219">
@@ -8238,7 +8035,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Дуб Винтаж Оксид  5194 SN</t>
+          <t>Мармара Голубая 5515 BS</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -8247,10 +8044,10 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>3509</v>
+        <v>3630</v>
       </c>
       <c r="E220" t="n">
-        <v>2132.97</v>
+        <v>2194.11</v>
       </c>
       <c r="F220" t="inlineStr"/>
       <c r="H220">
@@ -8266,7 +8063,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Дуб Венге  6495 BS</t>
+          <t>Мидия 5982 BS</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8275,10 +8072,10 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>3267</v>
+        <v>3113</v>
       </c>
       <c r="E221" t="n">
-        <v>2010.69</v>
+        <v>1932.88</v>
       </c>
       <c r="F221" t="inlineStr"/>
       <c r="H221">
@@ -8294,7 +8091,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Дуб Горный светлый 740 PR</t>
+          <t>Миндаль 0564 PE</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -8303,10 +8100,10 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>3267</v>
+        <v>3300</v>
       </c>
       <c r="E222" t="n">
-        <v>2010.69</v>
+        <v>2027.37</v>
       </c>
       <c r="F222" t="inlineStr"/>
       <c r="H222">
@@ -8322,7 +8119,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Дуб Золотой Craft K003 PW</t>
+          <t>Океан  0245 SU</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8331,10 +8128,10 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>3289</v>
+        <v>3630</v>
       </c>
       <c r="E223" t="n">
-        <v>2021.81</v>
+        <v>2194.11</v>
       </c>
       <c r="F223" t="inlineStr"/>
       <c r="H223">
@@ -8350,7 +8147,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Дуб Кофейный Urban K007 PW</t>
+          <t>Оранжевый 132 PE</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8359,10 +8156,10 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>3289</v>
+        <v>3344</v>
       </c>
       <c r="E224" t="n">
-        <v>2021.81</v>
+        <v>2049.6</v>
       </c>
       <c r="F224" t="inlineStr"/>
       <c r="H224">
@@ -8378,7 +8175,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Дуб Лисса 8925 BS</t>
+          <t>Песочный 515 PE</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8387,10 +8184,10 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>3322</v>
+        <v>3289</v>
       </c>
       <c r="E225" t="n">
-        <v>2038.48</v>
+        <v>2021.81</v>
       </c>
       <c r="F225" t="inlineStr"/>
       <c r="H225">
@@ -8406,7 +8203,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Дуб Молочный 8622 PR</t>
+          <t>Роза  8534 BS</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -8415,10 +8212,10 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>3267</v>
+        <v>3630</v>
       </c>
       <c r="E226" t="n">
-        <v>2010.69</v>
+        <v>2194.11</v>
       </c>
       <c r="F226" t="inlineStr"/>
       <c r="H226">
@@ -8434,7 +8231,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Дуб Нагано 8431 SN</t>
+          <t>Сатин  7045 SU</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -8443,10 +8240,10 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>3289</v>
+        <v>3630</v>
       </c>
       <c r="E227" t="n">
-        <v>2021.81</v>
+        <v>2194.11</v>
       </c>
       <c r="F227" t="inlineStr"/>
       <c r="H227">
@@ -8462,7 +8259,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Дуб Сонома Светлый  3025 SN</t>
+          <t>Серый Камень 112 PE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8471,10 +8268,10 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>3267</v>
+        <v>3289</v>
       </c>
       <c r="E228" t="n">
-        <v>2010.69</v>
+        <v>2021.81</v>
       </c>
       <c r="F228" t="inlineStr"/>
       <c r="H228">
@@ -8490,7 +8287,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Дуб Серый Craft K002 PW</t>
+          <t>Слоновая кость 514 РЕ</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8518,7 +8315,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Дуб Табачный Craft K004 PW</t>
+          <t>Солнечный Свет (Желтый) 134 BS</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8527,10 +8324,10 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>3289</v>
+        <v>3344</v>
       </c>
       <c r="E230" t="n">
-        <v>2021.81</v>
+        <v>2049.6</v>
       </c>
       <c r="F230" t="inlineStr"/>
       <c r="H230">
@@ -8546,7 +8343,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Дуб Устричный Urban K005 PW</t>
+          <t>Темный Коричневый  182 BS</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8555,10 +8352,10 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>3289</v>
+        <v>3344</v>
       </c>
       <c r="E231" t="n">
-        <v>2021.81</v>
+        <v>2049.6</v>
       </c>
       <c r="F231" t="inlineStr"/>
       <c r="H231">
@@ -8569,12 +8366,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ЛДСП Кроношпан Contempo</t>
+          <t>ЛДСП Кроношпан Color</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Дуб Экспрессив Бронзовый  K090 PW</t>
+          <t>Титан (Платина) 859 SM</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8583,10 +8380,10 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>3289</v>
+        <v>3344</v>
       </c>
       <c r="E232" t="n">
-        <v>2021.81</v>
+        <v>2049.6</v>
       </c>
       <c r="F232" t="inlineStr"/>
       <c r="H232">
@@ -8597,12 +8394,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ЛДСП Кроношпан Contempo</t>
+          <t>ЛДСП Кроношпан Color</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Дуб Экспрессив Песочный  K076 PW</t>
+          <t>Титан (Платина) 859 /РЕ</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8611,10 +8408,10 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>3289</v>
+        <v>3344</v>
       </c>
       <c r="E233" t="n">
-        <v>2021.81</v>
+        <v>2049.6</v>
       </c>
       <c r="F233" t="inlineStr"/>
       <c r="H233">
@@ -8625,12 +8422,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ЛДСП Кроношпан Contempo</t>
+          <t>ЛДСП Кроношпан Color</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Дуб Янтарный Urban K006 PW</t>
+          <t>Черный Шагрень 190 PE</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8658,7 +8455,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Клен 375 PR</t>
+          <t>Артвуд Светлый  К083 SN</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -8667,10 +8464,10 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>3267</v>
+        <v>3531</v>
       </c>
       <c r="E235" t="n">
-        <v>2010.69</v>
+        <v>2144.08</v>
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="H235">
@@ -8686,7 +8483,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Коко Бола 8995 BS</t>
+          <t>Артвуд Темный  К084 SN</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -8695,10 +8492,10 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>3322</v>
+        <v>3531</v>
       </c>
       <c r="E236" t="n">
-        <v>2038.48</v>
+        <v>2144.08</v>
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="H236">
@@ -8714,7 +8511,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Морское Дерево Винтаж K015 PW</t>
+          <t>Бук Артизан Перламутровый  К012 SU</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -8723,10 +8520,10 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>3289</v>
+        <v>3531</v>
       </c>
       <c r="E237" t="n">
-        <v>2021.81</v>
+        <v>2144.08</v>
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="H237">
@@ -8742,7 +8539,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Морское Дерево Карбон K016 PW</t>
+          <t>Бук Артизан Пеcочный К013 SU</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -8751,10 +8548,10 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>3289</v>
+        <v>3531</v>
       </c>
       <c r="E238" t="n">
-        <v>2021.81</v>
+        <v>2144.08</v>
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="H238">
@@ -8770,7 +8567,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Ольха горская 1912 PR</t>
+          <t>Бук Артизан Трюфельный К013 SU</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -8779,10 +8576,10 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>3267</v>
+        <v>3531</v>
       </c>
       <c r="E239" t="n">
-        <v>2010.69</v>
+        <v>2144.08</v>
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="H239">
@@ -8798,7 +8595,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Орех 729 PR</t>
+          <t>Блэквуд Ячменный K021 SN</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -8807,10 +8604,10 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>3267</v>
+        <v>3531</v>
       </c>
       <c r="E240" t="n">
-        <v>2010.69</v>
+        <v>2144.08</v>
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="H240">
@@ -8826,7 +8623,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Ночи Гварнери  9455 PR</t>
+          <t>Блэквуд Сатиновый K022 SN</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -8835,10 +8632,10 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>3344</v>
+        <v>3531</v>
       </c>
       <c r="E241" t="n">
-        <v>2049.6</v>
+        <v>2144.08</v>
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="H241">
@@ -8854,7 +8651,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Орех Каминный Select 020 PW</t>
+          <t>Венге Винтаж 7648 SN</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -8863,10 +8660,10 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>3289</v>
+        <v>3465</v>
       </c>
       <c r="E242" t="n">
-        <v>2021.81</v>
+        <v>2110.74</v>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="H242">
@@ -8882,7 +8679,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Орех Опера 481 BS</t>
+          <t>Гикори Роккфорд Натуральный  К086 PW</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -8891,10 +8688,10 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>3267</v>
+        <v>3531</v>
       </c>
       <c r="E243" t="n">
-        <v>2010.69</v>
+        <v>2144.08</v>
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="H243">
@@ -8910,7 +8707,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Орех Лион Светлый 9614 BS</t>
+          <t>Гикори Роккфорд Светлый К085 PW</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -8919,10 +8716,10 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>3344</v>
+        <v>3531</v>
       </c>
       <c r="E244" t="n">
-        <v>2049.6</v>
+        <v>2144.08</v>
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="H244">
@@ -8938,7 +8735,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Орех Мария Луиза (Итальянский) 9490 PR</t>
+          <t>Гикори Роккфорд Темный К087</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -8947,10 +8744,10 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>3267</v>
+        <v>3531</v>
       </c>
       <c r="E245" t="n">
-        <v>2010.69</v>
+        <v>2144.08</v>
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="H245">
@@ -8966,7 +8763,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Орех Светлый Select K008 PW</t>
+          <t>Дуб Бурбон  К082 PW</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -8975,10 +8772,10 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>3289</v>
+        <v>3531</v>
       </c>
       <c r="E246" t="n">
-        <v>2021.81</v>
+        <v>2144.08</v>
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="H246">
@@ -8994,7 +8791,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Орех Темный Select K009 PW</t>
+          <t>Дуб Каменный 5527 SN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -9003,10 +8800,10 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>3289</v>
+        <v>3531</v>
       </c>
       <c r="E247" t="n">
-        <v>2021.81</v>
+        <v>2144.08</v>
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="H247">
@@ -9022,7 +8819,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Орех Тьеполо 8953 SU</t>
+          <t>Дуб Клабхаус Серый  К079 PW</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9031,10 +8828,10 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>3344</v>
+        <v>3465</v>
       </c>
       <c r="E248" t="n">
-        <v>2049.6</v>
+        <v>2110.74</v>
       </c>
       <c r="F248" t="inlineStr"/>
       <c r="H248">
@@ -9050,7 +8847,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Ночи Экко 9459 PR</t>
+          <t>Дуб Приморский Белый  К080 PW</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -9059,10 +8856,10 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>3267</v>
+        <v>3465</v>
       </c>
       <c r="E249" t="n">
-        <v>2010.69</v>
+        <v>2110.74</v>
       </c>
       <c r="F249" t="inlineStr"/>
       <c r="H249">
@@ -9078,7 +8875,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Яблоня Локарно 1972 BS</t>
+          <t>Дуб Приморский Сатиновый K081 PW</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9087,10 +8884,10 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>3267</v>
+        <v>3465</v>
       </c>
       <c r="E250" t="n">
-        <v>2010.69</v>
+        <v>2110.74</v>
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="H250">
@@ -9106,7 +8903,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Ясень Таормина 8503 BS</t>
+          <t>Дуб Славония 5501 SN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -9115,10 +8912,10 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>3344</v>
+        <v>3531</v>
       </c>
       <c r="E251" t="n">
-        <v>2049.6</v>
+        <v>2144.08</v>
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="H251">
@@ -9134,7 +8931,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Ясень Шимо Светлый  3356 BS</t>
+          <t>Дуб Эндгрейн необработанный  К105 PW</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -9143,10 +8940,10 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>3267</v>
+        <v>3531</v>
       </c>
       <c r="E252" t="n">
-        <v>2010.69</v>
+        <v>2144.08</v>
       </c>
       <c r="F252" t="inlineStr"/>
       <c r="H252">
@@ -9162,7 +8959,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Ясень Шимо Темный 3357 PR</t>
+          <t>Дуб Эндгрейн Элегантный K107 PW</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9171,10 +8968,10 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>3267</v>
+        <v>3531</v>
       </c>
       <c r="E253" t="n">
-        <v>2010.69</v>
+        <v>2144.08</v>
       </c>
       <c r="F253" t="inlineStr"/>
       <c r="H253">
@@ -9190,7 +8987,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Белый (Влагостойкая ДСП) 101 SM</t>
+          <t>Зебрано Нюанс 8656 SN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9199,10 +8996,10 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>3729</v>
+        <v>3465</v>
       </c>
       <c r="E254" t="n">
-        <v>2244.13</v>
+        <v>2110.74</v>
       </c>
       <c r="F254" t="inlineStr"/>
       <c r="H254">
@@ -9218,7 +9015,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Алюминий 881 PE</t>
+          <t>Зебрано Сахара 8657 SN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9227,10 +9024,10 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>3344</v>
+        <v>3465</v>
       </c>
       <c r="E255" t="n">
-        <v>2049.6</v>
+        <v>2110.74</v>
       </c>
       <c r="F255" t="inlineStr"/>
       <c r="H255">
@@ -9246,7 +9043,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Антрацит  164 PE</t>
+          <t>Камень Светлый (Ателье) 4298 SU</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9255,10 +9052,10 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>3289</v>
+        <v>3531</v>
       </c>
       <c r="E256" t="n">
-        <v>2021.81</v>
+        <v>2144.08</v>
       </c>
       <c r="F256" t="inlineStr"/>
       <c r="H256">
@@ -9274,7 +9071,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Бежевый 522 PE</t>
+          <t>Камень Темный (Ателье) 4299 SU</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -9283,10 +9080,10 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>3289</v>
+        <v>3531</v>
       </c>
       <c r="E257" t="n">
-        <v>2021.81</v>
+        <v>2144.08</v>
       </c>
       <c r="F257" t="inlineStr"/>
       <c r="H257">
@@ -9302,7 +9099,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Белый Бриллиант 8681 SM</t>
+          <t>Крослайн Карамель 8362 SD/SU</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -9311,10 +9108,10 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>3608</v>
+        <v>3641</v>
       </c>
       <c r="E258" t="n">
-        <v>2182.99</v>
+        <v>2199.66</v>
       </c>
       <c r="F258" t="inlineStr"/>
       <c r="H258">
@@ -9330,7 +9127,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Белый Снег 8685 SN</t>
+          <t>Крослайн Латте 8361 SD/SU</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -9339,10 +9136,10 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>3729</v>
+        <v>3641</v>
       </c>
       <c r="E259" t="n">
-        <v>2244.13</v>
+        <v>2199.66</v>
       </c>
       <c r="F259" t="inlineStr"/>
       <c r="H259">
@@ -9358,7 +9155,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Белый Снег 8685 SM</t>
+          <t>Орегон 5529 SD/SU</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9367,10 +9164,10 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>3663</v>
+        <v>3641</v>
       </c>
       <c r="E260" t="n">
-        <v>2210.78</v>
+        <v>2199.66</v>
       </c>
       <c r="F260" t="inlineStr"/>
       <c r="H260">
@@ -9386,7 +9183,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Белый Фасадный 101 SM/РЕ</t>
+          <t>Пельтро  К108 SU</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -9414,7 +9211,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Ваниль 9569 PE</t>
+          <t>Северное Дерево Светлое 8508 SN</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9423,10 +9220,10 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>3300</v>
+        <v>3465</v>
       </c>
       <c r="E262" t="n">
-        <v>2027.37</v>
+        <v>2110.74</v>
       </c>
       <c r="F262" t="inlineStr"/>
       <c r="H262">
@@ -9442,7 +9239,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Зеленая Мамба  7190 BS</t>
+          <t>Северное Дерево Темное  8509 SN</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -9451,10 +9248,10 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>3630</v>
+        <v>3465</v>
       </c>
       <c r="E263" t="n">
-        <v>2194.11</v>
+        <v>2110.74</v>
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="H263">
@@ -9470,7 +9267,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Зеленый Лайм 5519 BS</t>
+          <t>Скандинавское Дерево Белое  К088 PW</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9479,10 +9276,10 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>3630</v>
+        <v>3465</v>
       </c>
       <c r="E264" t="n">
-        <v>2194.11</v>
+        <v>2110.74</v>
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="H264">
@@ -9493,12 +9290,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ЛДСП Кроношпан Trends</t>
+          <t>ЛДСП Кроношпан Contempo</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Кашемир 5981 BS</t>
+          <t>Cкандинавское Дерево Серое К089 PW</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -9507,10 +9304,10 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>3289</v>
+        <v>3150</v>
       </c>
       <c r="E265" t="n">
-        <v>2021.81</v>
+        <v>1951.58</v>
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="H265">
@@ -9521,12 +9318,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ЛДСП Кроношпан Trends</t>
+          <t>ЛДСП Кроношпан Contempo</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Капри Синий (Голубой) 121 BS</t>
+          <t>Сосна Белая Loft K010 SN</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -9535,10 +9332,10 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>3344</v>
+        <v>3465</v>
       </c>
       <c r="E266" t="n">
-        <v>2049.6</v>
+        <v>2110.74</v>
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="H266">
@@ -9549,12 +9346,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ЛДСП Кроношпан Trends</t>
+          <t>ЛДСП Кроношпан Contempo</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Королевский Синий 125 BS</t>
+          <t>Сосна Кремовая Loft  K011 SN</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -9563,10 +9360,10 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>3344</v>
+        <v>3465</v>
       </c>
       <c r="E267" t="n">
-        <v>2049.6</v>
+        <v>2110.74</v>
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="H267">
@@ -9577,12 +9374,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ЛДСП Кроношпан Trends</t>
+          <t>ЛДСП Кроношпан Contempo</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Керамический Красный  К098 SU</t>
+          <t>Файнлайн Светлый 8547 SN</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -9591,10 +9388,10 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>3630</v>
+        <v>3465</v>
       </c>
       <c r="E268" t="n">
-        <v>2194.11</v>
+        <v>2110.74</v>
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="H268">
@@ -9605,12 +9402,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ЛДСП Кроношпан Trends</t>
+          <t>ЛДСП Кроношпан Contempo</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Кобальт Серый  6299 BS</t>
+          <t>Файнлайн темный 8548 SN</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -9619,378 +9416,14 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>3630</v>
+        <v>3465</v>
       </c>
       <c r="E269" t="n">
-        <v>2194.11</v>
+        <v>2110.74</v>
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="H269">
         <f>IF(D269="","",ROUND(D269/IF(G269="",5.796,G269)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Красный 149 BS</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D270" t="n">
-        <v>3344</v>
-      </c>
-      <c r="E270" t="n">
-        <v>2049.6</v>
-      </c>
-      <c r="F270" t="inlineStr"/>
-      <c r="H270">
-        <f>IF(D270="","",ROUND(D270/IF(G270="",5.796,G270)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Красный Чили 7113 BS</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D271" t="n">
-        <v>3630</v>
-      </c>
-      <c r="E271" t="n">
-        <v>2194.11</v>
-      </c>
-      <c r="F271" t="inlineStr"/>
-      <c r="H271">
-        <f>IF(D271="","",ROUND(D271/IF(G271="",5.796,G271)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Красный Оксид  9551 PE</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D272" t="n">
-        <v>3344</v>
-      </c>
-      <c r="E272" t="n">
-        <v>2049.6</v>
-      </c>
-      <c r="F272" t="inlineStr"/>
-      <c r="H272">
-        <f>IF(D272="","",ROUND(D272/IF(G272="",5.796,G272)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Кремовый 7031 PE</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D273" t="n">
-        <v>3300</v>
-      </c>
-      <c r="E273" t="n">
-        <v>2027.37</v>
-      </c>
-      <c r="F273" t="inlineStr"/>
-      <c r="H273">
-        <f>IF(D273="","",ROUND(D273/IF(G273="",5.796,G273)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Лаванда 8536 BS</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D274" t="n">
-        <v>3630</v>
-      </c>
-      <c r="E274" t="n">
-        <v>2194.11</v>
-      </c>
-      <c r="F274" t="inlineStr"/>
-      <c r="H274">
-        <f>IF(D274="","",ROUND(D274/IF(G274="",5.796,G274)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Лате(Темный) 7166 BS</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D275" t="n">
-        <v>3630</v>
-      </c>
-      <c r="E275" t="n">
-        <v>2194.11</v>
-      </c>
-      <c r="F275" t="inlineStr"/>
-      <c r="H275">
-        <f>IF(D275="","",ROUND(D275/IF(G275="",5.796,G275)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Лимонный Сорбет 7123 BS</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D276" t="n">
-        <v>3344</v>
-      </c>
-      <c r="E276" t="n">
-        <v>2049.6</v>
-      </c>
-      <c r="F276" t="inlineStr"/>
-      <c r="H276">
-        <f>IF(D276="","",ROUND(D276/IF(G276="",5.796,G276)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Макиато (Лате) 8533 BS</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D277" t="n">
-        <v>3344</v>
-      </c>
-      <c r="E277" t="n">
-        <v>2049.6</v>
-      </c>
-      <c r="F277" t="inlineStr"/>
-      <c r="H277">
-        <f>IF(D277="","",ROUND(D277/IF(G277="",5.796,G277)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Мармара Голубая 5515 BS</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D278" t="n">
-        <v>3630</v>
-      </c>
-      <c r="E278" t="n">
-        <v>2194.11</v>
-      </c>
-      <c r="F278" t="inlineStr"/>
-      <c r="H278">
-        <f>IF(D278="","",ROUND(D278/IF(G278="",5.796,G278)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Мидия 5982 BS</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D279" t="n">
-        <v>3113</v>
-      </c>
-      <c r="E279" t="n">
-        <v>1932.88</v>
-      </c>
-      <c r="F279" t="inlineStr"/>
-      <c r="H279">
-        <f>IF(D279="","",ROUND(D279/IF(G279="",5.796,G279)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Миндаль 0564 PE</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D280" t="n">
-        <v>3300</v>
-      </c>
-      <c r="E280" t="n">
-        <v>2027.37</v>
-      </c>
-      <c r="F280" t="inlineStr"/>
-      <c r="H280">
-        <f>IF(D280="","",ROUND(D280/IF(G280="",5.796,G280)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Океан  0245 SU</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D281" t="n">
-        <v>3630</v>
-      </c>
-      <c r="E281" t="n">
-        <v>2194.11</v>
-      </c>
-      <c r="F281" t="inlineStr"/>
-      <c r="H281">
-        <f>IF(D281="","",ROUND(D281/IF(G281="",5.796,G281)*1.2+150,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>ЛДСП Кроношпан Trends</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Оранжевый 132 PE</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="D282" t="n">
-        <v>3344</v>
-      </c>
-      <c r="E282" t="n">
-        <v>2049.6</v>
-      </c>
-      <c r="F282" t="inlineStr"/>
-      <c r="H282">
-        <f>IF(D282="","",ROUND(D282/IF(G282="",5.796,G282)*1.2+150,0))</f>
         <v/>
       </c>
     </row>
